--- a/Prelims/SampleUpload.xlsx
+++ b/Prelims/SampleUpload.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ashwath\Own\ram\prelimsapplications\FNTUpdate\Prelims\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Madhu\audit\Prelims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CF969D-985E-499A-B5E2-EC21AFDF9058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521D8903-3914-48DC-94B9-ED1F05460E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{305D408E-FE0D-4A11-ACE7-022B48A32D2C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{305D408E-FE0D-4A11-ACE7-022B48A32D2C}"/>
   </bookViews>
   <sheets>
     <sheet name="All Orders" sheetId="1" r:id="rId1"/>
@@ -109,9 +109,6 @@
     <t>COUNTY</t>
   </si>
   <si>
-    <t>RECEIVEDDATETIME</t>
-  </si>
-  <si>
     <t>Updates</t>
   </si>
   <si>
@@ -395,6 +392,9 @@
   </si>
   <si>
     <t>NO</t>
+  </si>
+  <si>
+    <t>RECEIVEDDATETIME(MM-DD-YYYY)</t>
   </si>
 </sst>
 </file>
@@ -816,16 +816,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED8DC6F8-1A52-44B3-9D62-6A1325B9930E}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.81640625" customWidth="1"/>
+    <col min="7" max="7" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -845,13 +845,13 @@
         <v>23</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -862,19 +862,19 @@
         <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -885,16 +885,16 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -905,16 +905,16 @@
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -925,16 +925,16 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -945,16 +945,16 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -965,16 +965,16 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -985,16 +985,16 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1005,16 +1005,16 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1025,16 +1025,16 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1045,16 +1045,16 @@
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1065,16 +1065,16 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1085,16 +1085,16 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1114,16 +1114,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7ED2E3C-E67F-40A8-91FC-2993CF6D78C8}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1134,24 +1134,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C01236C-B277-4B5A-8257-01B508AE0321}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1162,199 +1162,199 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3790EB6-E34F-43F7-8DC2-4100BB220D01}">
   <dimension ref="A1:A38"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="75.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="75.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1365,301 +1365,301 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0CA21E-FD09-4C1A-A2F8-DFCE0A455336}">
   <dimension ref="A1:A59"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
